--- a/docs/cadrage/Mercredi/equipe-27-product-backlog-v.4.0.xlsx
+++ b/docs/cadrage/Mercredi/equipe-27-product-backlog-v.4.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flore\Documents\APOCALIPSSI\IPSSI_APOCAL_KIT\docs\cadrage\Mercredi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5B4F23-3B7D-4E45-8523-6A4A4872E711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C961DEB6-583B-4425-8EED-2D76994D88E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
